--- a/highschoolrank/rank.xlsx
+++ b/highschoolrank/rank.xlsx
@@ -462,20 +462,16 @@
           <t>清华大学</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
+      <c r="C2" t="n">
+        <v>96</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="E2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -487,20 +483,16 @@
           <t>北京大学</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>83.0</t>
-        </is>
+      <c r="C3" t="n">
+        <v>83</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>98.9</t>
-        </is>
+      <c r="E3" t="n">
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -512,20 +504,16 @@
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
+      <c r="C4" t="n">
+        <v>80</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>88.8</t>
-        </is>
+      <c r="E4" t="n">
+        <v>88.8</v>
       </c>
     </row>
     <row r="5">
@@ -537,20 +525,16 @@
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
+      <c r="C5" t="n">
+        <v>79</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>90.6</t>
-        </is>
+      <c r="E5" t="n">
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +546,16 @@
           <t>复旦大学</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
+      <c r="C6" t="n">
+        <v>71</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>90.4</t>
-        </is>
+      <c r="E6" t="n">
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -587,20 +567,16 @@
           <t>南京大学</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
+      <c r="C7" t="n">
+        <v>66</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>90.7</t>
-        </is>
+      <c r="E7" t="n">
+        <v>90.7</v>
       </c>
     </row>
     <row r="8">
@@ -612,20 +588,16 @@
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
+      <c r="C8" t="n">
+        <v>65</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>90.1</t>
-        </is>
+      <c r="E8" t="n">
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -637,20 +609,16 @@
           <t>哈尔滨工业大学</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
+      <c r="C9" t="n">
+        <v>63</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>80.9</t>
-        </is>
+      <c r="E9" t="n">
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -662,20 +630,16 @@
           <t>华中科技大学</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
+      <c r="C10" t="n">
+        <v>63</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>83.5</t>
-        </is>
+      <c r="E10" t="n">
+        <v>83.5</v>
       </c>
     </row>
     <row r="11">
@@ -687,20 +651,16 @@
           <t>中山大学</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
+      <c r="C11" t="n">
+        <v>62</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>81.8</t>
-        </is>
+      <c r="E11" t="n">
+        <v>81.8</v>
       </c>
     </row>
     <row r="12">
@@ -712,20 +672,16 @@
           <t>东南大学</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
+      <c r="C12" t="n">
+        <v>61</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="E12" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="13">
@@ -737,20 +693,16 @@
           <t>天津大学</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
+      <c r="C13" t="n">
+        <v>61</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>85.8</t>
-        </is>
+      <c r="E13" t="n">
+        <v>85.8</v>
       </c>
     </row>
     <row r="14">
@@ -762,20 +714,16 @@
           <t>同济大学</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
+      <c r="C14" t="n">
+        <v>60</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>87.5</t>
-        </is>
+      <c r="E14" t="n">
+        <v>87.5</v>
       </c>
     </row>
     <row r="15">
@@ -787,20 +735,16 @@
           <t>北京航空航天大学</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
+      <c r="C15" t="n">
+        <v>60</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>88.5</t>
-        </is>
+      <c r="E15" t="n">
+        <v>88.5</v>
       </c>
     </row>
     <row r="16">
@@ -812,20 +756,16 @@
           <t>四川大学</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
+      <c r="C16" t="n">
+        <v>59</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>77.3</t>
-        </is>
+      <c r="E16" t="n">
+        <v>77.3</v>
       </c>
     </row>
     <row r="17">
@@ -837,20 +777,16 @@
           <t>武汉大学</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
+      <c r="C17" t="n">
+        <v>59</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>84.7</t>
-        </is>
+      <c r="E17" t="n">
+        <v>84.7</v>
       </c>
     </row>
     <row r="18">
@@ -862,20 +798,16 @@
           <t>西安交通大学</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
+      <c r="C18" t="n">
+        <v>59</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>85.2</t>
-        </is>
+      <c r="E18" t="n">
+        <v>85.2</v>
       </c>
     </row>
     <row r="19">
@@ -887,20 +819,16 @@
           <t>南开大学</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
+      <c r="C19" t="n">
+        <v>58</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
+      <c r="E19" t="n">
+        <v>88.7</v>
       </c>
     </row>
     <row r="20">
@@ -912,20 +840,16 @@
           <t>大连理工大学</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
+      <c r="C20" t="n">
+        <v>57</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>79.1</t>
-        </is>
+      <c r="E20" t="n">
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -937,20 +861,16 @@
           <t>山东大学</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
+      <c r="C21" t="n">
+        <v>56</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>76.3</t>
-        </is>
+      <c r="E21" t="n">
+        <v>76.3</v>
       </c>
     </row>
     <row r="22">
@@ -962,20 +882,16 @@
           <t>华南理工大学</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
+      <c r="C22" t="n">
+        <v>56</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>76.1</t>
-        </is>
+      <c r="E22" t="n">
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -987,20 +903,16 @@
           <t>吉林大学</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
+      <c r="C23" t="n">
+        <v>56</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>77.4</t>
-        </is>
+      <c r="E23" t="n">
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1012,20 +924,16 @@
           <t>厦门大学</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
+      <c r="C24" t="n">
+        <v>55</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>83.4</t>
-        </is>
+      <c r="E24" t="n">
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1037,20 +945,16 @@
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
+      <c r="C25" t="n">
+        <v>55</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>86.1</t>
-        </is>
+      <c r="E25" t="n">
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1062,20 +966,16 @@
           <t>北京理工大学</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
+      <c r="C26" t="n">
+        <v>54</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="E26" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="27">
@@ -1087,20 +987,16 @@
           <t>苏州大学</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
+      <c r="C27" t="n">
+        <v>53</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>71.5</t>
-        </is>
+      <c r="E27" t="n">
+        <v>71.5</v>
       </c>
     </row>
     <row r="28">
@@ -1112,20 +1008,16 @@
           <t>中南大学</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+      <c r="C28" t="n">
+        <v>52</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>75.9</t>
-        </is>
+      <c r="E28" t="n">
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1137,20 +1029,16 @@
           <t>北京科技大学</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+      <c r="C29" t="n">
+        <v>52</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
+      <c r="E29" t="n">
+        <v>76.5</v>
       </c>
     </row>
     <row r="30">
@@ -1162,20 +1050,16 @@
           <t>南京航空航天大学</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+      <c r="C30" t="n">
+        <v>52</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>76.9</t>
-        </is>
+      <c r="E30" t="n">
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1187,20 +1071,16 @@
           <t>华东理工大学</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+      <c r="C31" t="n">
+        <v>52</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
+      <c r="E31" t="n">
+        <v>73.8</v>
       </c>
     </row>
   </sheetData>
@@ -1253,20 +1133,16 @@
           <t>清华大学</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1076.1</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1076.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>36.1</t>
-        </is>
+      <c r="E2" t="n">
+        <v>36.1</v>
       </c>
     </row>
     <row r="3">
@@ -1278,20 +1154,16 @@
           <t>北京大学</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1027.7</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1027.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
+      <c r="E3" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -1303,20 +1175,16 @@
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>868.9</t>
-        </is>
+      <c r="C4" t="n">
+        <v>868.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
+      <c r="E4" t="n">
+        <v>35.1</v>
       </c>
     </row>
     <row r="5">
@@ -1328,20 +1196,16 @@
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>851.7</t>
-        </is>
+      <c r="C5" t="n">
+        <v>851.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>35.7</t>
-        </is>
+      <c r="E5" t="n">
+        <v>35.7</v>
       </c>
     </row>
     <row r="6">
@@ -1353,20 +1217,16 @@
           <t>复旦大学</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>788.4</t>
-        </is>
+      <c r="C6" t="n">
+        <v>788.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
+      <c r="E6" t="n">
+        <v>36.8</v>
       </c>
     </row>
     <row r="7">
@@ -1378,20 +1238,16 @@
           <t>南京大学</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>707.8</t>
-        </is>
+      <c r="C7" t="n">
+        <v>707.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
+      <c r="E7" t="n">
+        <v>36.8</v>
       </c>
     </row>
     <row r="8">
@@ -1403,20 +1259,16 @@
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
+      <c r="C8" t="n">
+        <v>637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="E8" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -1428,20 +1280,16 @@
           <t>武汉大学</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>629.2</t>
-        </is>
+      <c r="C9" t="n">
+        <v>629.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>33.8</t>
-        </is>
+      <c r="E9" t="n">
+        <v>33.8</v>
       </c>
     </row>
     <row r="10">
@@ -1453,20 +1301,16 @@
           <t>华中科技大学</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>628.9</t>
-        </is>
+      <c r="C10" t="n">
+        <v>628.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
+      <c r="E10" t="n">
+        <v>32.8</v>
       </c>
     </row>
     <row r="11">
@@ -1478,20 +1322,16 @@
           <t>西安交通大学</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>598.5</t>
-        </is>
+      <c r="C11" t="n">
+        <v>598.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>34.6</t>
-        </is>
+      <c r="E11" t="n">
+        <v>34.6</v>
       </c>
     </row>
     <row r="12">
@@ -1503,20 +1343,16 @@
           <t>北京航空航天大学</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>585.4</t>
-        </is>
+      <c r="C12" t="n">
+        <v>585.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>33.5</t>
-        </is>
+      <c r="E12" t="n">
+        <v>33.5</v>
       </c>
     </row>
     <row r="13">
@@ -1528,20 +1364,16 @@
           <t>中山大学</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>585.2</t>
-        </is>
+      <c r="C13" t="n">
+        <v>585.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
+      <c r="E13" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -1553,20 +1385,16 @@
           <t>北京理工大学</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>582.4</t>
-        </is>
+      <c r="C14" t="n">
+        <v>582.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>33.5</t>
-        </is>
+      <c r="E14" t="n">
+        <v>33.5</v>
       </c>
     </row>
     <row r="15">
@@ -1578,20 +1406,16 @@
           <t>哈尔滨工业大学</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>576.4</t>
-        </is>
+      <c r="C15" t="n">
+        <v>576.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
+      <c r="E15" t="n">
+        <v>32.6</v>
       </c>
     </row>
     <row r="16">
@@ -1603,20 +1427,16 @@
           <t>四川大学</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>576.3</t>
-        </is>
+      <c r="C16" t="n">
+        <v>576.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>32.1</t>
-        </is>
+      <c r="E16" t="n">
+        <v>32.1</v>
       </c>
     </row>
     <row r="17">
@@ -1628,20 +1448,16 @@
           <t>东南大学</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>575.0</t>
-        </is>
+      <c r="C17" t="n">
+        <v>575</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>34.9</t>
-        </is>
+      <c r="E17" t="n">
+        <v>34.9</v>
       </c>
     </row>
     <row r="18">
@@ -1653,20 +1469,16 @@
           <t>中国人民大学</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>558.0</t>
-        </is>
+      <c r="C18" t="n">
+        <v>558</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>33.7</t>
-        </is>
+      <c r="E18" t="n">
+        <v>33.7</v>
       </c>
     </row>
     <row r="19">
@@ -1678,20 +1490,16 @@
           <t>同济大学</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>547.7</t>
-        </is>
+      <c r="C19" t="n">
+        <v>547.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>35.2</t>
-        </is>
+      <c r="E19" t="n">
+        <v>35.2</v>
       </c>
     </row>
     <row r="20">
@@ -1703,20 +1511,16 @@
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>543.8</t>
-        </is>
+      <c r="C20" t="n">
+        <v>543.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>32.1</t>
-        </is>
+      <c r="E20" t="n">
+        <v>32.1</v>
       </c>
     </row>
     <row r="21">
@@ -1728,20 +1532,16 @@
           <t>天津大学</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>528.5</t>
-        </is>
+      <c r="C21" t="n">
+        <v>528.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
+      <c r="E21" t="n">
+        <v>33.4</v>
       </c>
     </row>
     <row r="22">
@@ -1753,20 +1553,16 @@
           <t>西北工业大学</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>513.7</t>
-        </is>
+      <c r="C22" t="n">
+        <v>513.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>33.1</t>
-        </is>
+      <c r="E22" t="n">
+        <v>33.1</v>
       </c>
     </row>
     <row r="23">
@@ -1778,20 +1574,16 @@
           <t>山东大学</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>513.4</t>
-        </is>
+      <c r="C23" t="n">
+        <v>513.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>29.9</t>
-        </is>
+      <c r="E23" t="n">
+        <v>29.9</v>
       </c>
     </row>
     <row r="24">
@@ -1803,20 +1595,16 @@
           <t>南开大学</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>512.2</t>
-        </is>
+      <c r="C24" t="n">
+        <v>512.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>32.3</t>
-        </is>
+      <c r="E24" t="n">
+        <v>32.3</v>
       </c>
     </row>
     <row r="25">
@@ -1828,20 +1616,16 @@
           <t>厦门大学</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>504.8</t>
-        </is>
+      <c r="C25" t="n">
+        <v>504.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>32.5</t>
-        </is>
+      <c r="E25" t="n">
+        <v>32.5</v>
       </c>
     </row>
     <row r="26">
@@ -1853,20 +1637,16 @@
           <t>中国农业大学</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>499.2</t>
-        </is>
+      <c r="C26" t="n">
+        <v>499.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>农业</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>31.7</t>
-        </is>
+      <c r="E26" t="n">
+        <v>31.7</v>
       </c>
     </row>
     <row r="27">
@@ -1878,20 +1658,16 @@
           <t>吉林大学</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>486.0</t>
-        </is>
+      <c r="C27" t="n">
+        <v>486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
+      <c r="E27" t="n">
+        <v>30.7</v>
       </c>
     </row>
     <row r="28">
@@ -1903,20 +1679,16 @@
           <t>中南大学</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>485.3</t>
-        </is>
+      <c r="C28" t="n">
+        <v>485.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>31.3</t>
-        </is>
+      <c r="E28" t="n">
+        <v>31.3</v>
       </c>
     </row>
     <row r="29">
@@ -1928,20 +1700,16 @@
           <t>大连理工大学</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>469.5</t>
-        </is>
+      <c r="C29" t="n">
+        <v>469.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>31.3</t>
-        </is>
+      <c r="E29" t="n">
+        <v>31.3</v>
       </c>
     </row>
     <row r="30">
@@ -1953,20 +1721,16 @@
           <t>湖南大学</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>466.4</t>
-        </is>
+      <c r="C30" t="n">
+        <v>466.4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
+      <c r="E30" t="n">
+        <v>30.7</v>
       </c>
     </row>
     <row r="31">
@@ -1978,20 +1742,16 @@
           <t>华东师范大学</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>460.1</t>
-        </is>
+      <c r="C31" t="n">
+        <v>460.1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
+      <c r="E31" t="n">
+        <v>32.8</v>
       </c>
     </row>
   </sheetData>
@@ -2044,20 +1804,16 @@
           <t>清华大学</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1087.1</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1087.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>36.2</t>
-        </is>
+      <c r="E2" t="n">
+        <v>36.2</v>
       </c>
     </row>
     <row r="3">
@@ -2069,20 +1825,16 @@
           <t>北京大学</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1036.3</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1036.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
+      <c r="E3" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -2094,20 +1846,16 @@
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>895.6</t>
-        </is>
+      <c r="C4" t="n">
+        <v>895.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>34.9</t>
-        </is>
+      <c r="E4" t="n">
+        <v>34.9</v>
       </c>
     </row>
     <row r="5">
@@ -2119,20 +1867,16 @@
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>894.2</t>
-        </is>
+      <c r="C5" t="n">
+        <v>894.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>35.7</t>
-        </is>
+      <c r="E5" t="n">
+        <v>35.7</v>
       </c>
     </row>
     <row r="6">
@@ -2144,20 +1888,16 @@
           <t>复旦大学</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>792.4</t>
-        </is>
+      <c r="C6" t="n">
+        <v>792.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
+      <c r="E6" t="n">
+        <v>36.8</v>
       </c>
     </row>
     <row r="7">
@@ -2169,20 +1909,16 @@
           <t>南京大学</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>708.5</t>
-        </is>
+      <c r="C7" t="n">
+        <v>708.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
+      <c r="E7" t="n">
+        <v>36.8</v>
       </c>
     </row>
     <row r="8">
@@ -2194,20 +1930,16 @@
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>653.1</t>
-        </is>
+      <c r="C8" t="n">
+        <v>653.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="E8" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -2219,20 +1951,16 @@
           <t>武汉大学</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>638.7</t>
-        </is>
+      <c r="C9" t="n">
+        <v>638.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>32.3</t>
-        </is>
+      <c r="E9" t="n">
+        <v>32.3</v>
       </c>
     </row>
     <row r="10">
@@ -2244,20 +1972,16 @@
           <t>华中科技大学</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>638.0</t>
-        </is>
+      <c r="C10" t="n">
+        <v>638</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
+      <c r="E10" t="n">
+        <v>32.6</v>
       </c>
     </row>
     <row r="11">
@@ -2269,20 +1993,16 @@
           <t>西安交通大学</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>620.8</t>
-        </is>
+      <c r="C11" t="n">
+        <v>620.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
+      <c r="E11" t="n">
+        <v>33.2</v>
       </c>
     </row>
     <row r="12">
@@ -2294,20 +2014,16 @@
           <t>北京航空航天大学</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>612.8</t>
-        </is>
+      <c r="C12" t="n">
+        <v>612.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>33.8</t>
-        </is>
+      <c r="E12" t="n">
+        <v>33.8</v>
       </c>
     </row>
     <row r="13">
@@ -2319,20 +2035,16 @@
           <t>哈尔滨工业大学</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>607.7</t>
-        </is>
+      <c r="C13" t="n">
+        <v>607.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
+      <c r="E13" t="n">
+        <v>32.4</v>
       </c>
     </row>
     <row r="14">
@@ -2344,20 +2056,16 @@
           <t>中山大学</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>597.6</t>
-        </is>
+      <c r="C14" t="n">
+        <v>597.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
+      <c r="E14" t="n">
+        <v>31.5</v>
       </c>
     </row>
     <row r="15">
@@ -2369,20 +2077,16 @@
           <t>北京理工大学</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>595.4</t>
-        </is>
+      <c r="C15" t="n">
+        <v>595.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>33.3</t>
-        </is>
+      <c r="E15" t="n">
+        <v>33.3</v>
       </c>
     </row>
     <row r="16">
@@ -2394,20 +2098,16 @@
           <t>东南大学</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>592.3</t>
-        </is>
+      <c r="C16" t="n">
+        <v>592.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
+      <c r="E16" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2419,20 +2119,16 @@
           <t>四川大学</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>581.3</t>
-        </is>
+      <c r="C17" t="n">
+        <v>581.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>32.5</t>
-        </is>
+      <c r="E17" t="n">
+        <v>32.5</v>
       </c>
     </row>
     <row r="18">
@@ -2444,20 +2140,16 @@
           <t>中国人民大学</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>558.1</t>
-        </is>
+      <c r="C18" t="n">
+        <v>558.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
+      <c r="E18" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -2469,20 +2161,16 @@
           <t>同济大学</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>556.6</t>
-        </is>
+      <c r="C19" t="n">
+        <v>556.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>34.9</t>
-        </is>
+      <c r="E19" t="n">
+        <v>34.9</v>
       </c>
     </row>
     <row r="20">
@@ -2494,20 +2182,16 @@
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>553.2</t>
-        </is>
+      <c r="C20" t="n">
+        <v>553.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
+      <c r="E20" t="n">
+        <v>32.6</v>
       </c>
     </row>
     <row r="21">
@@ -2519,20 +2203,16 @@
           <t>天津大学</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>544.2</t>
-        </is>
+      <c r="C21" t="n">
+        <v>544.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
+      <c r="E21" t="n">
+        <v>33.4</v>
       </c>
     </row>
     <row r="22">
@@ -2544,20 +2224,16 @@
           <t>南开大学</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>528.8</t>
-        </is>
+      <c r="C22" t="n">
+        <v>528.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>32.5</t>
-        </is>
+      <c r="E22" t="n">
+        <v>32.5</v>
       </c>
     </row>
     <row r="23">
@@ -2569,20 +2245,16 @@
           <t>山东大学</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>527.1</t>
-        </is>
+      <c r="C23" t="n">
+        <v>527.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>29.9</t>
-        </is>
+      <c r="E23" t="n">
+        <v>29.9</v>
       </c>
     </row>
     <row r="24">
@@ -2594,20 +2266,16 @@
           <t>西北工业大学</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>519.2</t>
-        </is>
+      <c r="C24" t="n">
+        <v>519.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
+      <c r="E24" t="n">
+        <v>32.9</v>
       </c>
     </row>
     <row r="25">
@@ -2619,20 +2287,16 @@
           <t>中国农业大学</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>519.1</t>
-        </is>
+      <c r="C25" t="n">
+        <v>519.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>农业</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
+      <c r="E25" t="n">
+        <v>31.5</v>
       </c>
     </row>
     <row r="26">
@@ -2644,20 +2308,16 @@
           <t>厦门大学</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>512.5</t>
-        </is>
+      <c r="C26" t="n">
+        <v>512.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
+      <c r="E26" t="n">
+        <v>32.7</v>
       </c>
     </row>
     <row r="27">
@@ -2669,20 +2329,16 @@
           <t>吉林大学</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>498.2</t>
-        </is>
+      <c r="C27" t="n">
+        <v>498.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
+      <c r="E27" t="n">
+        <v>30.6</v>
       </c>
     </row>
     <row r="28">
@@ -2694,20 +2350,16 @@
           <t>中南大学</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>497.0</t>
-        </is>
+      <c r="C28" t="n">
+        <v>497</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
+      <c r="E28" t="n">
+        <v>30.6</v>
       </c>
     </row>
     <row r="29">
@@ -2719,20 +2371,16 @@
           <t>大连理工大学</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>495.4</t>
-        </is>
+      <c r="C29" t="n">
+        <v>495.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
+      <c r="E29" t="n">
+        <v>31.5</v>
       </c>
     </row>
     <row r="30">
@@ -2744,20 +2392,16 @@
           <t>华东师范大学</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>469.1</t>
-        </is>
+      <c r="C30" t="n">
+        <v>469.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
+      <c r="E30" t="n">
+        <v>32.8</v>
       </c>
     </row>
     <row r="31">
@@ -2769,20 +2413,16 @@
           <t>南方科技大学</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>466.9</t>
-        </is>
+      <c r="C31" t="n">
+        <v>466.9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>33.8</t>
-        </is>
+      <c r="E31" t="n">
+        <v>33.8</v>
       </c>
     </row>
   </sheetData>
@@ -2835,20 +2475,16 @@
           <t>清华大学</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
+      <c r="C2" t="n">
+        <v>94</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="E2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -2860,20 +2496,16 @@
           <t>北京大学</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
+      <c r="C3" t="n">
+        <v>81</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>96.1</t>
-        </is>
+      <c r="E3" t="n">
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2885,20 +2517,16 @@
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
+      <c r="C4" t="n">
+        <v>78</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>87.2</t>
-        </is>
+      <c r="E4" t="n">
+        <v>87.2</v>
       </c>
     </row>
     <row r="5">
@@ -2910,20 +2538,16 @@
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
+      <c r="C5" t="n">
+        <v>77</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>89.4</t>
-        </is>
+      <c r="E5" t="n">
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2935,20 +2559,16 @@
           <t>复旦大学</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
+      <c r="C6" t="n">
+        <v>71</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>91.8</t>
-        </is>
+      <c r="E6" t="n">
+        <v>91.8</v>
       </c>
     </row>
     <row r="7">
@@ -2960,20 +2580,16 @@
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
+      <c r="C7" t="n">
+        <v>66</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>91.9</t>
-        </is>
+      <c r="E7" t="n">
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2985,20 +2601,16 @@
           <t>南京大学</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
+      <c r="C8" t="n">
+        <v>65</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>87.1</t>
-        </is>
+      <c r="E8" t="n">
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3010,20 +2622,16 @@
           <t>华中科技大学</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
+      <c r="C9" t="n">
+        <v>63</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>80.6</t>
-        </is>
+      <c r="E9" t="n">
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -3035,20 +2643,16 @@
           <t>中山大学</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
+      <c r="C10" t="n">
+        <v>63</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>81.1</t>
-        </is>
+      <c r="E10" t="n">
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -3060,20 +2664,16 @@
           <t>哈尔滨工业大学</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
+      <c r="C11" t="n">
+        <v>62</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
+      <c r="E11" t="n">
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -3085,20 +2685,16 @@
           <t>同济大学</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
+      <c r="C12" t="n">
+        <v>61</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>86.2</t>
-        </is>
+      <c r="E12" t="n">
+        <v>86.2</v>
       </c>
     </row>
     <row r="13">
@@ -3110,20 +2706,16 @@
           <t>东南大学</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
+      <c r="C13" t="n">
+        <v>60</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>80.5</t>
-        </is>
+      <c r="E13" t="n">
+        <v>80.5</v>
       </c>
     </row>
     <row r="14">
@@ -3135,20 +2727,16 @@
           <t>武汉大学</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
+      <c r="C14" t="n">
+        <v>58</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>82.5</t>
-        </is>
+      <c r="E14" t="n">
+        <v>82.5</v>
       </c>
     </row>
     <row r="15">
@@ -3160,20 +2748,16 @@
           <t>北京航空航天大学</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
+      <c r="C15" t="n">
+        <v>58</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>85.5</t>
-        </is>
+      <c r="E15" t="n">
+        <v>85.5</v>
       </c>
     </row>
     <row r="16">
@@ -3185,20 +2769,16 @@
           <t>南开大学</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
+      <c r="C16" t="n">
+        <v>58</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
+      <c r="E16" t="n">
+        <v>86.5</v>
       </c>
     </row>
     <row r="17">
@@ -3210,20 +2790,16 @@
           <t>四川大学</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
+      <c r="C17" t="n">
+        <v>57</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
+      <c r="E17" t="n">
+        <v>74.5</v>
       </c>
     </row>
     <row r="18">
@@ -3235,20 +2811,16 @@
           <t>西安交通大学</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
+      <c r="C18" t="n">
+        <v>57</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>82.2</t>
-        </is>
+      <c r="E18" t="n">
+        <v>82.2</v>
       </c>
     </row>
     <row r="19">
@@ -3260,20 +2832,16 @@
           <t>天津大学</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
+      <c r="C19" t="n">
+        <v>56</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>82.7</t>
-        </is>
+      <c r="E19" t="n">
+        <v>82.7</v>
       </c>
     </row>
     <row r="20">
@@ -3285,20 +2853,16 @@
           <t>华南理工大学</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
+      <c r="C20" t="n">
+        <v>56</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>75.6</t>
-        </is>
+      <c r="E20" t="n">
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3310,20 +2874,16 @@
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
+      <c r="C21" t="n">
+        <v>55</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>82.5</t>
-        </is>
+      <c r="E21" t="n">
+        <v>82.5</v>
       </c>
     </row>
     <row r="22">
@@ -3335,20 +2895,16 @@
           <t>厦门大学</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
+      <c r="C22" t="n">
+        <v>55</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>81.5</t>
-        </is>
+      <c r="E22" t="n">
+        <v>81.5</v>
       </c>
     </row>
     <row r="23">
@@ -3360,20 +2916,16 @@
           <t>山东大学</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
+      <c r="C23" t="n">
+        <v>54</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
+      <c r="E23" t="n">
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -3385,20 +2937,16 @@
           <t>大连理工大学</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
+      <c r="C24" t="n">
+        <v>54</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="E24" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="25">
@@ -3410,20 +2958,16 @@
           <t>吉林大学</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
+      <c r="C25" t="n">
+        <v>54</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
+      <c r="E25" t="n">
+        <v>72.3</v>
       </c>
     </row>
     <row r="26">
@@ -3435,20 +2979,16 @@
           <t>北京理工大学</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
+      <c r="C26" t="n">
+        <v>53</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>80.4</t>
-        </is>
+      <c r="E26" t="n">
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3460,20 +3000,16 @@
           <t>中南大学</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+      <c r="C27" t="n">
+        <v>52</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>74.2</t>
-        </is>
+      <c r="E27" t="n">
+        <v>74.2</v>
       </c>
     </row>
     <row r="28">
@@ -3485,20 +3021,16 @@
           <t>对外经济贸易大学</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+      <c r="C28" t="n">
+        <v>52</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>财经</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
+      <c r="E28" t="n">
+        <v>84.5</v>
       </c>
     </row>
     <row r="29">
@@ -3510,20 +3042,16 @@
           <t>苏州大学</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+      <c r="C29" t="n">
+        <v>52</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
+      <c r="E29" t="n">
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3535,20 +3063,16 @@
           <t>中国人民大学</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+      <c r="C30" t="n">
+        <v>52</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="E30" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="31">
@@ -3560,20 +3084,16 @@
           <t>西北工业大学</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
+      <c r="C31" t="n">
+        <v>51</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>75.5</t>
-        </is>
+      <c r="E31" t="n">
+        <v>75.5</v>
       </c>
     </row>
   </sheetData>
@@ -3626,20 +3146,16 @@
           <t>清华大学</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>95.3</t>
-        </is>
+      <c r="C2" t="n">
+        <v>95.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="E2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -3651,20 +3167,16 @@
           <t>北京大学</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>78.6</t>
-        </is>
+      <c r="C3" t="n">
+        <v>78.59999999999999</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>96.4</t>
-        </is>
+      <c r="E3" t="n">
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -3676,20 +3188,16 @@
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>73.9</t>
-        </is>
+      <c r="C4" t="n">
+        <v>73.90000000000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>86.3</t>
-        </is>
+      <c r="E4" t="n">
+        <v>86.3</v>
       </c>
     </row>
     <row r="5">
@@ -3701,20 +3209,16 @@
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
+      <c r="C5" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>90.5</t>
-        </is>
+      <c r="E5" t="n">
+        <v>90.5</v>
       </c>
     </row>
     <row r="6">
@@ -3726,20 +3230,16 @@
           <t>复旦大学</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
+      <c r="C6" t="n">
+        <v>66</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
+      <c r="E6" t="n">
+        <v>91.5</v>
       </c>
     </row>
     <row r="7">
@@ -3751,20 +3251,16 @@
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>61.9</t>
-        </is>
+      <c r="C7" t="n">
+        <v>61.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>92.1</t>
-        </is>
+      <c r="E7" t="n">
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -3776,20 +3272,16 @@
           <t>南京大学</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>59.8</t>
-        </is>
+      <c r="C8" t="n">
+        <v>59.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>88.4</t>
-        </is>
+      <c r="E8" t="n">
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -3801,20 +3293,16 @@
           <t>华中科技大学</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>59.1</t>
-        </is>
+      <c r="C9" t="n">
+        <v>59.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
+      <c r="E9" t="n">
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -3826,20 +3314,16 @@
           <t>中山大学</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>58.6</t>
-        </is>
+      <c r="C10" t="n">
+        <v>58.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>81.1</t>
-        </is>
+      <c r="E10" t="n">
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -3851,20 +3335,16 @@
           <t>哈尔滨工业大学</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
+      <c r="C11" t="n">
+        <v>57.4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>78.2</t>
-        </is>
+      <c r="E11" t="n">
+        <v>78.2</v>
       </c>
     </row>
     <row r="12">
@@ -3876,20 +3356,16 @@
           <t>同济大学</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>56.4</t>
-        </is>
+      <c r="C12" t="n">
+        <v>56.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+      <c r="E12" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="13">
@@ -3901,20 +3377,16 @@
           <t>武汉大学</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>55.5</t>
-        </is>
+      <c r="C13" t="n">
+        <v>55.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>84.4</t>
-        </is>
+      <c r="E13" t="n">
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -3926,20 +3398,16 @@
           <t>东南大学</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>55.3</t>
-        </is>
+      <c r="C14" t="n">
+        <v>55.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>81.8</t>
-        </is>
+      <c r="E14" t="n">
+        <v>81.8</v>
       </c>
     </row>
     <row r="15">
@@ -3951,20 +3419,16 @@
           <t>西安交通大学</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
+      <c r="C15" t="n">
+        <v>54.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>83.6</t>
-        </is>
+      <c r="E15" t="n">
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -3976,20 +3440,16 @@
           <t>北京航空航天大学</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
+      <c r="C16" t="n">
+        <v>54</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>85.4</t>
-        </is>
+      <c r="E16" t="n">
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -4001,20 +3461,16 @@
           <t>南开大学</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>53.9</t>
-        </is>
+      <c r="C17" t="n">
+        <v>53.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
+      <c r="E17" t="n">
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -4026,20 +3482,16 @@
           <t>四川大学</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
+      <c r="C18" t="n">
+        <v>53.3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>75.7</t>
-        </is>
+      <c r="E18" t="n">
+        <v>75.7</v>
       </c>
     </row>
     <row r="19">
@@ -4051,20 +3503,16 @@
           <t>天津大学</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
+      <c r="C19" t="n">
+        <v>52.4</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>82.5</t>
-        </is>
+      <c r="E19" t="n">
+        <v>82.5</v>
       </c>
     </row>
     <row r="20">
@@ -4076,20 +3524,16 @@
           <t>华南理工大学</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>51.8</t>
-        </is>
+      <c r="C20" t="n">
+        <v>51.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>74.8</t>
-        </is>
+      <c r="E20" t="n">
+        <v>74.8</v>
       </c>
     </row>
     <row r="21">
@@ -4101,20 +3545,16 @@
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
+      <c r="C21" t="n">
+        <v>51.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>85.1</t>
-        </is>
+      <c r="E21" t="n">
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -4126,20 +3566,16 @@
           <t>北京理工大学</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
+      <c r="C22" t="n">
+        <v>51.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>82.1</t>
-        </is>
+      <c r="E22" t="n">
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -4151,20 +3587,16 @@
           <t>厦门大学</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>50.9</t>
-        </is>
+      <c r="C23" t="n">
+        <v>50.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
+      <c r="E23" t="n">
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -4176,20 +3608,16 @@
           <t>吉林大学</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
+      <c r="C24" t="n">
+        <v>50.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>74.4</t>
-        </is>
+      <c r="E24" t="n">
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -4201,20 +3629,16 @@
           <t>山东大学</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
+      <c r="C25" t="n">
+        <v>50</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>73.4</t>
-        </is>
+      <c r="E25" t="n">
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -4226,20 +3650,16 @@
           <t>大连理工大学</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
+      <c r="C26" t="n">
+        <v>49.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>75.8</t>
-        </is>
+      <c r="E26" t="n">
+        <v>75.8</v>
       </c>
     </row>
     <row r="27">
@@ -4251,20 +3671,16 @@
           <t>中南大学</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>49.5</t>
-        </is>
+      <c r="C27" t="n">
+        <v>49.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="E27" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="28">
@@ -4276,20 +3692,16 @@
           <t>苏州大学</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
+      <c r="C28" t="n">
+        <v>48.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>69.5</t>
-        </is>
+      <c r="E28" t="n">
+        <v>69.5</v>
       </c>
     </row>
     <row r="29">
@@ -4301,20 +3713,16 @@
           <t>对外经济贸易大学</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>47.7</t>
-        </is>
+      <c r="C29" t="n">
+        <v>47.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>财经</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>84.2</t>
-        </is>
+      <c r="E29" t="n">
+        <v>84.2</v>
       </c>
     </row>
     <row r="30">
@@ -4326,20 +3734,16 @@
           <t>西北工业大学</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
+      <c r="C30" t="n">
+        <v>47.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>77.1</t>
-        </is>
+      <c r="E30" t="n">
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -4351,20 +3755,16 @@
           <t>中国人民大学</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
+      <c r="C31" t="n">
+        <v>47.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>90.8</t>
-        </is>
+      <c r="E31" t="n">
+        <v>90.8</v>
       </c>
     </row>
   </sheetData>
@@ -4417,20 +3817,16 @@
           <t>清华大学</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>94.6</t>
-        </is>
+      <c r="C2" t="n">
+        <v>94.59999999999999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="E2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -4442,20 +3838,16 @@
           <t>北京大学</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
+      <c r="C3" t="n">
+        <v>76.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>95.2</t>
-        </is>
+      <c r="E3" t="n">
+        <v>95.2</v>
       </c>
     </row>
     <row r="4">
@@ -4467,20 +3859,16 @@
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
+      <c r="C4" t="n">
+        <v>72.90000000000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>84.2</t>
-        </is>
+      <c r="E4" t="n">
+        <v>84.2</v>
       </c>
     </row>
     <row r="5">
@@ -4492,20 +3880,16 @@
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>72.1</t>
-        </is>
+      <c r="C5" t="n">
+        <v>72.09999999999999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>91.1</t>
-        </is>
+      <c r="E5" t="n">
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -4517,20 +3901,16 @@
           <t>复旦大学</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
+      <c r="C6" t="n">
+        <v>65.59999999999999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
+      <c r="E6" t="n">
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -4542,20 +3922,16 @@
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
+      <c r="C7" t="n">
+        <v>60.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>91.1</t>
-        </is>
+      <c r="E7" t="n">
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -4567,20 +3943,16 @@
           <t>华中科技大学</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
+      <c r="C8" t="n">
+        <v>58.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>80.1</t>
-        </is>
+      <c r="E8" t="n">
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -4592,20 +3964,16 @@
           <t>南京大学</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
+      <c r="C9" t="n">
+        <v>58.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>86.2</t>
-        </is>
+      <c r="E9" t="n">
+        <v>86.2</v>
       </c>
     </row>
     <row r="10">
@@ -4617,20 +3985,16 @@
           <t>中山大学</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>58.2</t>
-        </is>
+      <c r="C10" t="n">
+        <v>58.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>79.7</t>
-        </is>
+      <c r="E10" t="n">
+        <v>79.7</v>
       </c>
     </row>
     <row r="11">
@@ -4642,20 +4006,16 @@
           <t>哈尔滨工业大学</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
+      <c r="C11" t="n">
+        <v>56.7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>76.6</t>
-        </is>
+      <c r="E11" t="n">
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -4667,20 +4027,16 @@
           <t>北京航空航天大学</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>56.3</t>
-        </is>
+      <c r="C12" t="n">
+        <v>56.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>86.9</t>
-        </is>
+      <c r="E12" t="n">
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -4692,20 +4048,16 @@
           <t>武汉大学</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
+      <c r="C13" t="n">
+        <v>56.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
+      <c r="E13" t="n">
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -4717,20 +4069,16 @@
           <t>同济大学</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>55.7</t>
-        </is>
+      <c r="C14" t="n">
+        <v>55.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>85.2</t>
-        </is>
+      <c r="E14" t="n">
+        <v>85.2</v>
       </c>
     </row>
     <row r="15">
@@ -4742,20 +4090,16 @@
           <t>西安交通大学</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
+      <c r="C15" t="n">
+        <v>55</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="E15" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -4767,20 +4111,16 @@
           <t>四川大学</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
+      <c r="C16" t="n">
+        <v>54.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="E16" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -4792,20 +4132,16 @@
           <t>北京理工大学</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
+      <c r="C17" t="n">
+        <v>54</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>79.7</t>
-        </is>
+      <c r="E17" t="n">
+        <v>79.7</v>
       </c>
     </row>
     <row r="18">
@@ -4817,20 +4153,16 @@
           <t>东南大学</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>53.6</t>
-        </is>
+      <c r="C18" t="n">
+        <v>53.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>79.4</t>
-        </is>
+      <c r="E18" t="n">
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -4842,20 +4174,16 @@
           <t>南开大学</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>52.8</t>
-        </is>
+      <c r="C19" t="n">
+        <v>52.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>83.9</t>
-        </is>
+      <c r="E19" t="n">
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -4867,20 +4195,16 @@
           <t>天津大学</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
+      <c r="C20" t="n">
+        <v>52.3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>80.1</t>
-        </is>
+      <c r="E20" t="n">
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -4892,20 +4216,16 @@
           <t>华南理工大学</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+      <c r="C21" t="n">
+        <v>52</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>73.4</t>
-        </is>
+      <c r="E21" t="n">
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -4917,20 +4237,16 @@
           <t>中南大学</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
+      <c r="C22" t="n">
+        <v>50.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>73.2</t>
-        </is>
+      <c r="E22" t="n">
+        <v>73.2</v>
       </c>
     </row>
     <row r="23">
@@ -4942,20 +4258,16 @@
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
+      <c r="C23" t="n">
+        <v>49.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>82.7</t>
-        </is>
+      <c r="E23" t="n">
+        <v>82.7</v>
       </c>
     </row>
     <row r="24">
@@ -4967,20 +4279,16 @@
           <t>山东大学</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
+      <c r="C24" t="n">
+        <v>49.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>71.3</t>
-        </is>
+      <c r="E24" t="n">
+        <v>71.3</v>
       </c>
     </row>
     <row r="25">
@@ -4992,20 +4300,16 @@
           <t>厦门大学</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
+      <c r="C25" t="n">
+        <v>49.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>75.3</t>
-        </is>
+      <c r="E25" t="n">
+        <v>75.3</v>
       </c>
     </row>
     <row r="26">
@@ -5017,20 +4321,16 @@
           <t>吉林大学</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>48.9</t>
-        </is>
+      <c r="C26" t="n">
+        <v>48.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
+      <c r="E26" t="n">
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -5042,20 +4342,16 @@
           <t>大连理工大学</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>48.6</t>
-        </is>
+      <c r="C27" t="n">
+        <v>48.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
+      <c r="E27" t="n">
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -5067,20 +4363,16 @@
           <t>电子科技大学</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>48.4</t>
-        </is>
+      <c r="C28" t="n">
+        <v>48.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
+      <c r="E28" t="n">
+        <v>73.8</v>
       </c>
     </row>
     <row r="29">
@@ -5092,20 +4384,16 @@
           <t>湖南大学</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
+      <c r="C29" t="n">
+        <v>48.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>71.7</t>
-        </is>
+      <c r="E29" t="n">
+        <v>71.7</v>
       </c>
     </row>
     <row r="30">
@@ -5117,20 +4405,16 @@
           <t>苏州大学</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
+      <c r="C30" t="n">
+        <v>47.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>64.7</t>
-        </is>
+      <c r="E30" t="n">
+        <v>64.7</v>
       </c>
     </row>
     <row r="31">
@@ -5142,20 +4426,16 @@
           <t>西北工业大学</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>46.7</t>
-        </is>
+      <c r="C31" t="n">
+        <v>46.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="E31" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -5208,20 +4488,16 @@
           <t>清华大学</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>852.5</t>
-        </is>
+      <c r="C2" t="n">
+        <v>852.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>38.2</t>
-        </is>
+      <c r="E2" t="n">
+        <v>38.2</v>
       </c>
     </row>
     <row r="3">
@@ -5233,20 +4509,16 @@
           <t>北京大学</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>746.7</t>
-        </is>
+      <c r="C3" t="n">
+        <v>746.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>36.1</t>
-        </is>
+      <c r="E3" t="n">
+        <v>36.1</v>
       </c>
     </row>
     <row r="4">
@@ -5258,20 +4530,16 @@
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>649.2</t>
-        </is>
+      <c r="C4" t="n">
+        <v>649.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>33.9</t>
-        </is>
+      <c r="E4" t="n">
+        <v>33.9</v>
       </c>
     </row>
     <row r="5">
@@ -5283,20 +4551,16 @@
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>625.9</t>
-        </is>
+      <c r="C5" t="n">
+        <v>625.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>35.4</t>
-        </is>
+      <c r="E5" t="n">
+        <v>35.4</v>
       </c>
     </row>
     <row r="6">
@@ -5308,20 +4572,16 @@
           <t>南京大学</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>566.1</t>
-        </is>
+      <c r="C6" t="n">
+        <v>566.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
+      <c r="E6" t="n">
+        <v>35.1</v>
       </c>
     </row>
     <row r="7">
@@ -5333,20 +4593,16 @@
           <t>复旦大学</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>556.7</t>
-        </is>
+      <c r="C7" t="n">
+        <v>556.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>36.6</t>
-        </is>
+      <c r="E7" t="n">
+        <v>36.6</v>
       </c>
     </row>
     <row r="8">
@@ -5358,20 +4614,16 @@
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>526.4</t>
-        </is>
+      <c r="C8" t="n">
+        <v>526.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="E8" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -5383,20 +4635,16 @@
           <t>华中科技大学</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>497.7</t>
-        </is>
+      <c r="C9" t="n">
+        <v>497.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>31.9</t>
-        </is>
+      <c r="E9" t="n">
+        <v>31.9</v>
       </c>
     </row>
     <row r="10">
@@ -5408,20 +4656,16 @@
           <t>武汉大学</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>488.0</t>
-        </is>
+      <c r="C10" t="n">
+        <v>488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>31.7</t>
-        </is>
+      <c r="E10" t="n">
+        <v>31.7</v>
       </c>
     </row>
     <row r="11">
@@ -5433,20 +4677,16 @@
           <t>中山大学</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>457.2</t>
-        </is>
+      <c r="C11" t="n">
+        <v>457.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>30.3</t>
-        </is>
+      <c r="E11" t="n">
+        <v>30.3</v>
       </c>
     </row>
     <row r="12">
@@ -5458,20 +4698,16 @@
           <t>西安交通大学</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>452.5</t>
-        </is>
+      <c r="C12" t="n">
+        <v>452.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
+      <c r="E12" t="n">
+        <v>34.3</v>
       </c>
     </row>
     <row r="13">
@@ -5483,20 +4719,16 @@
           <t>哈尔滨工业大学</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>450.2</t>
-        </is>
+      <c r="C13" t="n">
+        <v>450.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
+      <c r="E13" t="n">
+        <v>32.7</v>
       </c>
     </row>
     <row r="14">
@@ -5508,20 +4740,16 @@
           <t>北京航空航天大学</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>445.1</t>
-        </is>
+      <c r="C14" t="n">
+        <v>445.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
+      <c r="E14" t="n">
+        <v>32.8</v>
       </c>
     </row>
     <row r="15">
@@ -5533,20 +4761,16 @@
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>440.9</t>
-        </is>
+      <c r="C15" t="n">
+        <v>440.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
+      <c r="E15" t="n">
+        <v>34.8</v>
       </c>
     </row>
     <row r="16">
@@ -5558,20 +4782,16 @@
           <t>同济大学</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>439.0</t>
-        </is>
+      <c r="C16" t="n">
+        <v>439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
+      <c r="E16" t="n">
+        <v>33.4</v>
       </c>
     </row>
     <row r="17">
@@ -5583,20 +4803,16 @@
           <t>四川大学</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>435.7</t>
-        </is>
+      <c r="C17" t="n">
+        <v>435.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>32.5</t>
-        </is>
+      <c r="E17" t="n">
+        <v>32.5</v>
       </c>
     </row>
     <row r="18">
@@ -5608,20 +4824,16 @@
           <t>东南大学</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>432.7</t>
-        </is>
+      <c r="C18" t="n">
+        <v>432.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>33.7</t>
-        </is>
+      <c r="E18" t="n">
+        <v>33.7</v>
       </c>
     </row>
     <row r="19">
@@ -5633,20 +4845,16 @@
           <t>中国人民大学</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>409.7</t>
-        </is>
+      <c r="C19" t="n">
+        <v>409.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
+      <c r="E19" t="n">
+        <v>34.5</v>
       </c>
     </row>
     <row r="20">
@@ -5658,20 +4866,16 @@
           <t>南开大学</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>402.1</t>
-        </is>
+      <c r="C20" t="n">
+        <v>402.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
+      <c r="E20" t="n">
+        <v>32.4</v>
       </c>
     </row>
     <row r="21">
@@ -5683,20 +4887,16 @@
           <t>北京理工大学</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>395.6</t>
-        </is>
+      <c r="C21" t="n">
+        <v>395.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>31.9</t>
-        </is>
+      <c r="E21" t="n">
+        <v>31.9</v>
       </c>
     </row>
     <row r="22">
@@ -5708,20 +4908,16 @@
           <t>天津大学</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>390.3</t>
-        </is>
+      <c r="C22" t="n">
+        <v>390.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
+      <c r="E22" t="n">
+        <v>32.6</v>
       </c>
     </row>
     <row r="23">
@@ -5733,20 +4929,16 @@
           <t>山东大学</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>387.9</t>
-        </is>
+      <c r="C23" t="n">
+        <v>387.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
+      <c r="E23" t="n">
+        <v>28.8</v>
       </c>
     </row>
     <row r="24">
@@ -5758,20 +4950,16 @@
           <t>厦门大学</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>383.3</t>
-        </is>
+      <c r="C24" t="n">
+        <v>383.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
+      <c r="E24" t="n">
+        <v>32.7</v>
       </c>
     </row>
     <row r="25">
@@ -5783,20 +4971,16 @@
           <t>吉林大学</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>379.5</t>
-        </is>
+      <c r="C25" t="n">
+        <v>379.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>29.9</t>
-        </is>
+      <c r="E25" t="n">
+        <v>29.9</v>
       </c>
     </row>
     <row r="26">
@@ -5808,20 +4992,16 @@
           <t>华南理工大学</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>379.4</t>
-        </is>
+      <c r="C26" t="n">
+        <v>379.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
+      <c r="E26" t="n">
+        <v>30.4</v>
       </c>
     </row>
     <row r="27">
@@ -5833,20 +5013,16 @@
           <t>中南大学</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>378.6</t>
-        </is>
+      <c r="C27" t="n">
+        <v>378.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
+      <c r="E27" t="n">
+        <v>30.6</v>
       </c>
     </row>
     <row r="28">
@@ -5858,20 +5034,16 @@
           <t>大连理工大学</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>365.1</t>
-        </is>
+      <c r="C28" t="n">
+        <v>365.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>30.1</t>
-        </is>
+      <c r="E28" t="n">
+        <v>30.1</v>
       </c>
     </row>
     <row r="29">
@@ -5883,20 +5055,16 @@
           <t>西北工业大学</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>359.6</t>
-        </is>
+      <c r="C29" t="n">
+        <v>359.6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>32.5</t>
-        </is>
+      <c r="E29" t="n">
+        <v>32.5</v>
       </c>
     </row>
     <row r="30">
@@ -5908,20 +5076,16 @@
           <t>华东师范大学</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>358.0</t>
-        </is>
+      <c r="C30" t="n">
+        <v>358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
+      <c r="E30" t="n">
+        <v>32.6</v>
       </c>
     </row>
     <row r="31">
@@ -5933,20 +5097,16 @@
           <t>中国农业大学</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>351.5</t>
-        </is>
+      <c r="C31" t="n">
+        <v>351.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>农业</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>30.9</t>
-        </is>
+      <c r="E31" t="n">
+        <v>30.9</v>
       </c>
     </row>
   </sheetData>
@@ -5999,20 +5159,16 @@
           <t>清华大学</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>969.2</t>
-        </is>
+      <c r="C2" t="n">
+        <v>969.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
+      <c r="E2" t="n">
+        <v>37.9</v>
       </c>
     </row>
     <row r="3">
@@ -6024,20 +5180,16 @@
           <t>北京大学</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>855.3</t>
-        </is>
+      <c r="C3" t="n">
+        <v>855.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>36.1</t>
-        </is>
+      <c r="E3" t="n">
+        <v>36.1</v>
       </c>
     </row>
     <row r="4">
@@ -6049,20 +5201,16 @@
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>768.7</t>
-        </is>
+      <c r="C4" t="n">
+        <v>768.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
+      <c r="E4" t="n">
+        <v>34.3</v>
       </c>
     </row>
     <row r="5">
@@ -6074,20 +5222,16 @@
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>723.4</t>
-        </is>
+      <c r="C5" t="n">
+        <v>723.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>35.5</t>
-        </is>
+      <c r="E5" t="n">
+        <v>35.5</v>
       </c>
     </row>
     <row r="6">
@@ -6099,20 +5243,16 @@
           <t>南京大学</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>654.8</t>
-        </is>
+      <c r="C6" t="n">
+        <v>654.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
+      <c r="E6" t="n">
+        <v>35.1</v>
       </c>
     </row>
     <row r="7">
@@ -6124,20 +5264,16 @@
           <t>复旦大学</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>649.7</t>
-        </is>
+      <c r="C7" t="n">
+        <v>649.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>36.6</t>
-        </is>
+      <c r="E7" t="n">
+        <v>36.6</v>
       </c>
     </row>
     <row r="8">
@@ -6149,20 +5285,16 @@
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>577.0</t>
-        </is>
+      <c r="C8" t="n">
+        <v>577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="E8" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -6174,20 +5306,16 @@
           <t>华中科技大学</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>574.3</t>
-        </is>
+      <c r="C9" t="n">
+        <v>574.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>32.1</t>
-        </is>
+      <c r="E9" t="n">
+        <v>32.1</v>
       </c>
     </row>
     <row r="10">
@@ -6199,20 +5327,16 @@
           <t>武汉大学</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>567.9</t>
-        </is>
+      <c r="C10" t="n">
+        <v>567.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
+      <c r="E10" t="n">
+        <v>31.8</v>
       </c>
     </row>
     <row r="11">
@@ -6224,20 +5348,16 @@
           <t>西安交通大学</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>537.9</t>
-        </is>
+      <c r="C11" t="n">
+        <v>537.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
+      <c r="E11" t="n">
+        <v>34.5</v>
       </c>
     </row>
     <row r="12">
@@ -6249,20 +5369,16 @@
           <t>哈尔滨工业大学</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>522.6</t>
-        </is>
+      <c r="C12" t="n">
+        <v>522.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
+      <c r="E12" t="n">
+        <v>32.7</v>
       </c>
     </row>
     <row r="13">
@@ -6274,20 +5390,16 @@
           <t>中山大学</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>519.3</t>
-        </is>
+      <c r="C13" t="n">
+        <v>519.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>30.9</t>
-        </is>
+      <c r="E13" t="n">
+        <v>30.9</v>
       </c>
     </row>
     <row r="14">
@@ -6299,20 +5411,16 @@
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>518.3</t>
-        </is>
+      <c r="C14" t="n">
+        <v>518.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
+      <c r="E14" t="n">
+        <v>34.8</v>
       </c>
     </row>
     <row r="15">
@@ -6324,20 +5432,16 @@
           <t>四川大学</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>516.6</t>
-        </is>
+      <c r="C15" t="n">
+        <v>516.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
+      <c r="E15" t="n">
+        <v>30.7</v>
       </c>
     </row>
     <row r="16">
@@ -6349,20 +5453,16 @@
           <t>北京航空航天大学</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>513.8</t>
-        </is>
+      <c r="C16" t="n">
+        <v>513.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
+      <c r="E16" t="n">
+        <v>32.8</v>
       </c>
     </row>
     <row r="17">
@@ -6374,20 +5474,16 @@
           <t>同济大学</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>508.3</t>
-        </is>
+      <c r="C17" t="n">
+        <v>508.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
+      <c r="E17" t="n">
+        <v>33.2</v>
       </c>
     </row>
     <row r="18">
@@ -6399,20 +5495,16 @@
           <t>东南大学</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>488.1</t>
-        </is>
+      <c r="C18" t="n">
+        <v>488.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
+      <c r="E18" t="n">
+        <v>34.3</v>
       </c>
     </row>
     <row r="19">
@@ -6424,20 +5516,16 @@
           <t>中国人民大学</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>487.8</t>
-        </is>
+      <c r="C19" t="n">
+        <v>487.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
+      <c r="E19" t="n">
+        <v>34.5</v>
       </c>
     </row>
     <row r="20">
@@ -6449,20 +5537,16 @@
           <t>北京理工大学</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>474.0</t>
-        </is>
+      <c r="C20" t="n">
+        <v>474</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>32.3</t>
-        </is>
+      <c r="E20" t="n">
+        <v>32.3</v>
       </c>
     </row>
     <row r="21">
@@ -6474,20 +5558,16 @@
           <t>南开大学</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>465.3</t>
-        </is>
+      <c r="C21" t="n">
+        <v>465.3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
+      <c r="E21" t="n">
+        <v>31.5</v>
       </c>
     </row>
     <row r="22">
@@ -6499,20 +5579,16 @@
           <t>山东大学</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>447.0</t>
-        </is>
+      <c r="C22" t="n">
+        <v>447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
+      <c r="E22" t="n">
+        <v>28.8</v>
       </c>
     </row>
     <row r="23">
@@ -6524,20 +5600,16 @@
           <t>天津大学</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>444.3</t>
-        </is>
+      <c r="C23" t="n">
+        <v>444.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
+      <c r="E23" t="n">
+        <v>32.7</v>
       </c>
     </row>
     <row r="24">
@@ -6549,20 +5621,16 @@
           <t>中南大学</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>442.2</t>
-        </is>
+      <c r="C24" t="n">
+        <v>442.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
+      <c r="E24" t="n">
+        <v>30.8</v>
       </c>
     </row>
     <row r="25">
@@ -6574,20 +5642,16 @@
           <t>吉林大学</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>435.7</t>
-        </is>
+      <c r="C25" t="n">
+        <v>435.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
+      <c r="E25" t="n">
+        <v>30.4</v>
       </c>
     </row>
     <row r="26">
@@ -6599,20 +5663,16 @@
           <t>西北工业大学</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>430.5</t>
-        </is>
+      <c r="C26" t="n">
+        <v>430.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
+      <c r="E26" t="n">
+        <v>32.4</v>
       </c>
     </row>
     <row r="27">
@@ -6624,20 +5684,16 @@
           <t>厦门大学</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>427.8</t>
-        </is>
+      <c r="C27" t="n">
+        <v>427.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
+      <c r="E27" t="n">
+        <v>32.7</v>
       </c>
     </row>
     <row r="28">
@@ -6649,20 +5705,16 @@
           <t>华南理工大学</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>419.8</t>
-        </is>
+      <c r="C28" t="n">
+        <v>419.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
+      <c r="E28" t="n">
+        <v>30.5</v>
       </c>
     </row>
     <row r="29">
@@ -6674,20 +5726,16 @@
           <t>大连理工大学</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>418.2</t>
-        </is>
+      <c r="C29" t="n">
+        <v>418.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>30.2</t>
-        </is>
+      <c r="E29" t="n">
+        <v>30.2</v>
       </c>
     </row>
     <row r="30">
@@ -6699,20 +5747,16 @@
           <t>华东师范大学</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>401.8</t>
-        </is>
+      <c r="C30" t="n">
+        <v>401.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>35.2</t>
-        </is>
+      <c r="E30" t="n">
+        <v>35.2</v>
       </c>
     </row>
     <row r="31">
@@ -6724,20 +5768,16 @@
           <t>中国农业大学</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>400.4</t>
-        </is>
+      <c r="C31" t="n">
+        <v>400.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>农业</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
+      <c r="E31" t="n">
+        <v>31.8</v>
       </c>
     </row>
   </sheetData>
@@ -6790,20 +5830,16 @@
           <t>清华大学</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>999.4</t>
-        </is>
+      <c r="C2" t="n">
+        <v>999.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>37.6</t>
-        </is>
+      <c r="E2" t="n">
+        <v>37.6</v>
       </c>
     </row>
     <row r="3">
@@ -6815,20 +5851,16 @@
           <t>北京大学</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>912.5</t>
-        </is>
+      <c r="C3" t="n">
+        <v>912.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>34.4</t>
-        </is>
+      <c r="E3" t="n">
+        <v>34.4</v>
       </c>
     </row>
     <row r="4">
@@ -6840,20 +5872,16 @@
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>825.3</t>
-        </is>
+      <c r="C4" t="n">
+        <v>825.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>34.1</t>
-        </is>
+      <c r="E4" t="n">
+        <v>34.1</v>
       </c>
     </row>
     <row r="5">
@@ -6865,20 +5893,16 @@
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>783.3</t>
-        </is>
+      <c r="C5" t="n">
+        <v>783.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>35.5</t>
-        </is>
+      <c r="E5" t="n">
+        <v>35.5</v>
       </c>
     </row>
     <row r="6">
@@ -6890,20 +5914,16 @@
           <t>复旦大学</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>697.8</t>
-        </is>
+      <c r="C6" t="n">
+        <v>697.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>35.9</t>
-        </is>
+      <c r="E6" t="n">
+        <v>35.9</v>
       </c>
     </row>
     <row r="7">
@@ -6915,20 +5935,16 @@
           <t>南京大学</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>683.4</t>
-        </is>
+      <c r="C7" t="n">
+        <v>683.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>37.7</t>
-        </is>
+      <c r="E7" t="n">
+        <v>37.7</v>
       </c>
     </row>
     <row r="8">
@@ -6940,20 +5956,16 @@
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>609.9</t>
-        </is>
+      <c r="C8" t="n">
+        <v>609.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="E8" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -6965,20 +5977,16 @@
           <t>华中科技大学</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>609.3</t>
-        </is>
+      <c r="C9" t="n">
+        <v>609.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>32.3</t>
-        </is>
+      <c r="E9" t="n">
+        <v>32.3</v>
       </c>
     </row>
     <row r="10">
@@ -6990,20 +5998,16 @@
           <t>武汉大学</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>607.1</t>
-        </is>
+      <c r="C10" t="n">
+        <v>607.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
+      <c r="E10" t="n">
+        <v>32.8</v>
       </c>
     </row>
     <row r="11">
@@ -7015,20 +6019,16 @@
           <t>西安交通大学</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>570.2</t>
-        </is>
+      <c r="C11" t="n">
+        <v>570.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>34.2</t>
-        </is>
+      <c r="E11" t="n">
+        <v>34.2</v>
       </c>
     </row>
     <row r="12">
@@ -7040,20 +6040,16 @@
           <t>四川大学</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>561.7</t>
-        </is>
+      <c r="C12" t="n">
+        <v>561.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
+      <c r="E12" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -7065,20 +6061,16 @@
           <t>中山大学</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>559.4</t>
-        </is>
+      <c r="C13" t="n">
+        <v>559.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
+      <c r="E13" t="n">
+        <v>31.4</v>
       </c>
     </row>
     <row r="14">
@@ -7090,20 +6082,16 @@
           <t>哈尔滨工业大学</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>549.8</t>
-        </is>
+      <c r="C14" t="n">
+        <v>549.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
+      <c r="E14" t="n">
+        <v>32.7</v>
       </c>
     </row>
     <row r="15">
@@ -7115,20 +6103,16 @@
           <t>同济大学</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>548.4</t>
-        </is>
+      <c r="C15" t="n">
+        <v>548.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
+      <c r="E15" t="n">
+        <v>32.8</v>
       </c>
     </row>
     <row r="16">
@@ -7140,20 +6124,16 @@
           <t>北京航空航天大学</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>546.7</t>
-        </is>
+      <c r="C16" t="n">
+        <v>546.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
+      <c r="E16" t="n">
+        <v>33.2</v>
       </c>
     </row>
     <row r="17">
@@ -7165,20 +6145,16 @@
           <t>东南大学</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>538.5</t>
-        </is>
+      <c r="C17" t="n">
+        <v>538.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>34.9</t>
-        </is>
+      <c r="E17" t="n">
+        <v>34.9</v>
       </c>
     </row>
     <row r="18">
@@ -7190,20 +6166,16 @@
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>534.7</t>
-        </is>
+      <c r="C18" t="n">
+        <v>534.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>34.6</t>
-        </is>
+      <c r="E18" t="n">
+        <v>34.6</v>
       </c>
     </row>
     <row r="19">
@@ -7215,20 +6187,16 @@
           <t>北京理工大学</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>530.9</t>
-        </is>
+      <c r="C19" t="n">
+        <v>530.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>33.1</t>
-        </is>
+      <c r="E19" t="n">
+        <v>33.1</v>
       </c>
     </row>
     <row r="20">
@@ -7240,20 +6208,16 @@
           <t>中国人民大学</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>514.7</t>
-        </is>
+      <c r="C20" t="n">
+        <v>514.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>34.2</t>
-        </is>
+      <c r="E20" t="n">
+        <v>34.2</v>
       </c>
     </row>
     <row r="21">
@@ -7265,20 +6229,16 @@
           <t>南开大学</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>497.4</t>
-        </is>
+      <c r="C21" t="n">
+        <v>497.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>31.3</t>
-        </is>
+      <c r="E21" t="n">
+        <v>31.3</v>
       </c>
     </row>
     <row r="22">
@@ -7290,20 +6250,16 @@
           <t>天津大学</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>490.8</t>
-        </is>
+      <c r="C22" t="n">
+        <v>490.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
+      <c r="E22" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -7315,20 +6271,16 @@
           <t>山东大学</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>484.3</t>
-        </is>
+      <c r="C23" t="n">
+        <v>484.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
+      <c r="E23" t="n">
+        <v>29.2</v>
       </c>
     </row>
     <row r="24">
@@ -7340,20 +6292,16 @@
           <t>中南大学</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>475.8</t>
-        </is>
+      <c r="C24" t="n">
+        <v>475.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
+      <c r="E24" t="n">
+        <v>30.7</v>
       </c>
     </row>
     <row r="25">
@@ -7365,20 +6313,16 @@
           <t>西北工业大学</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>467.9</t>
-        </is>
+      <c r="C25" t="n">
+        <v>467.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
+      <c r="E25" t="n">
+        <v>32.7</v>
       </c>
     </row>
     <row r="26">
@@ -7390,20 +6334,16 @@
           <t>华南理工大学</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>466.7</t>
-        </is>
+      <c r="C26" t="n">
+        <v>466.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
+      <c r="E26" t="n">
+        <v>30.8</v>
       </c>
     </row>
     <row r="27">
@@ -7415,20 +6355,16 @@
           <t>厦门大学</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>458.8</t>
-        </is>
+      <c r="C27" t="n">
+        <v>458.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>33.7</t>
-        </is>
+      <c r="E27" t="n">
+        <v>33.7</v>
       </c>
     </row>
     <row r="28">
@@ -7440,20 +6376,16 @@
           <t>吉林大学</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>450.3</t>
-        </is>
+      <c r="C28" t="n">
+        <v>450.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>31.2</t>
-        </is>
+      <c r="E28" t="n">
+        <v>31.2</v>
       </c>
     </row>
     <row r="29">
@@ -7465,20 +6397,16 @@
           <t>华东师范大学</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>440.7</t>
-        </is>
+      <c r="C29" t="n">
+        <v>440.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
+      <c r="E29" t="n">
+        <v>32.6</v>
       </c>
     </row>
     <row r="30">
@@ -7490,20 +6418,16 @@
           <t>中国农业大学</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>433.7</t>
-        </is>
+      <c r="C30" t="n">
+        <v>433.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>农业</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>31.9</t>
-        </is>
+      <c r="E30" t="n">
+        <v>31.9</v>
       </c>
     </row>
     <row r="31">
@@ -7515,20 +6439,16 @@
           <t>电子科技大学</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>432.0</t>
-        </is>
+      <c r="C31" t="n">
+        <v>432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>32.3</t>
-        </is>
+      <c r="E31" t="n">
+        <v>32.3</v>
       </c>
     </row>
   </sheetData>
@@ -7581,20 +6501,16 @@
           <t>清华大学</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1004.1</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1004.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
+      <c r="E2" t="n">
+        <v>37.5</v>
       </c>
     </row>
     <row r="3">
@@ -7606,20 +6522,16 @@
           <t>北京大学</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>910.5</t>
-        </is>
+      <c r="C3" t="n">
+        <v>910.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
+      <c r="E3" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -7631,20 +6543,16 @@
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>822.9</t>
-        </is>
+      <c r="C4" t="n">
+        <v>822.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>35.9</t>
-        </is>
+      <c r="E4" t="n">
+        <v>35.9</v>
       </c>
     </row>
     <row r="5">
@@ -7656,20 +6564,16 @@
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>778.6</t>
-        </is>
+      <c r="C5" t="n">
+        <v>778.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>35.7</t>
-        </is>
+      <c r="E5" t="n">
+        <v>35.7</v>
       </c>
     </row>
     <row r="6">
@@ -7681,20 +6585,16 @@
           <t>复旦大学</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>712.4</t>
-        </is>
+      <c r="C6" t="n">
+        <v>712.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>36.5</t>
-        </is>
+      <c r="E6" t="n">
+        <v>36.5</v>
       </c>
     </row>
     <row r="7">
@@ -7706,20 +6606,16 @@
           <t>南京大学</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>676.2</t>
-        </is>
+      <c r="C7" t="n">
+        <v>676.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>37.7</t>
-        </is>
+      <c r="E7" t="n">
+        <v>37.7</v>
       </c>
     </row>
     <row r="8">
@@ -7731,20 +6627,16 @@
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>608.6</t>
-        </is>
+      <c r="C8" t="n">
+        <v>608.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="E8" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -7756,20 +6648,16 @@
           <t>华中科技大学</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>606.2</t>
-        </is>
+      <c r="C9" t="n">
+        <v>606.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>32.2</t>
-        </is>
+      <c r="E9" t="n">
+        <v>32.2</v>
       </c>
     </row>
     <row r="10">
@@ -7781,20 +6669,16 @@
           <t>武汉大学</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>599.1</t>
-        </is>
+      <c r="C10" t="n">
+        <v>599.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
+      <c r="E10" t="n">
+        <v>31.8</v>
       </c>
     </row>
     <row r="11">
@@ -7806,20 +6690,16 @@
           <t>西安交通大学</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>572.6</t>
-        </is>
+      <c r="C11" t="n">
+        <v>572.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>34.2</t>
-        </is>
+      <c r="E11" t="n">
+        <v>34.2</v>
       </c>
     </row>
     <row r="12">
@@ -7831,20 +6711,16 @@
           <t>中山大学</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>570.0</t>
-        </is>
+      <c r="C12" t="n">
+        <v>570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>31.1</t>
-        </is>
+      <c r="E12" t="n">
+        <v>31.1</v>
       </c>
     </row>
     <row r="13">
@@ -7856,20 +6732,16 @@
           <t>四川大学</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>546.9</t>
-        </is>
+      <c r="C13" t="n">
+        <v>546.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
+      <c r="E13" t="n">
+        <v>31.5</v>
       </c>
     </row>
     <row r="14">
@@ -7881,20 +6753,16 @@
           <t>哈尔滨工业大学</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>544.2</t>
-        </is>
+      <c r="C14" t="n">
+        <v>544.2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
+      <c r="E14" t="n">
+        <v>32.7</v>
       </c>
     </row>
     <row r="15">
@@ -7906,20 +6774,16 @@
           <t>北京航空航天大学</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>543.5</t>
-        </is>
+      <c r="C15" t="n">
+        <v>543.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
+      <c r="E15" t="n">
+        <v>33.4</v>
       </c>
     </row>
     <row r="16">
@@ -7931,20 +6795,16 @@
           <t>东南大学</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>532.3</t>
-        </is>
+      <c r="C16" t="n">
+        <v>532.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>35.4</t>
-        </is>
+      <c r="E16" t="n">
+        <v>35.4</v>
       </c>
     </row>
     <row r="17">
@@ -7956,20 +6816,16 @@
           <t>北京理工大学</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>529.3</t>
-        </is>
+      <c r="C17" t="n">
+        <v>529.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
+      <c r="E17" t="n">
+        <v>33.4</v>
       </c>
     </row>
     <row r="18">
@@ -7981,20 +6837,16 @@
           <t>同济大学</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>527.0</t>
-        </is>
+      <c r="C18" t="n">
+        <v>527</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
+      <c r="E18" t="n">
+        <v>33.2</v>
       </c>
     </row>
     <row r="19">
@@ -8006,20 +6858,16 @@
           <t>中国人民大学</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>526.3</t>
-        </is>
+      <c r="C19" t="n">
+        <v>526.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>34.7</t>
-        </is>
+      <c r="E19" t="n">
+        <v>34.7</v>
       </c>
     </row>
     <row r="20">
@@ -8031,20 +6879,16 @@
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>523.4</t>
-        </is>
+      <c r="C20" t="n">
+        <v>523.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
+      <c r="E20" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="21">
@@ -8056,20 +6900,16 @@
           <t>南开大学</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>490.4</t>
-        </is>
+      <c r="C21" t="n">
+        <v>490.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>31.7</t>
-        </is>
+      <c r="E21" t="n">
+        <v>31.7</v>
       </c>
     </row>
     <row r="22">
@@ -8081,20 +6921,16 @@
           <t>天津大学</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>480.5</t>
-        </is>
+      <c r="C22" t="n">
+        <v>480.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
+      <c r="E22" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -8106,20 +6942,16 @@
           <t>山东大学</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>472.8</t>
-        </is>
+      <c r="C23" t="n">
+        <v>472.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
+      <c r="E23" t="n">
+        <v>29.7</v>
       </c>
     </row>
     <row r="24">
@@ -8131,20 +6963,16 @@
           <t>中南大学</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>466.1</t>
-        </is>
+      <c r="C24" t="n">
+        <v>466.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
+      <c r="E24" t="n">
+        <v>30.7</v>
       </c>
     </row>
     <row r="25">
@@ -8156,20 +6984,16 @@
           <t>厦门大学</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>463.2</t>
-        </is>
+      <c r="C25" t="n">
+        <v>463.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>32.5</t>
-        </is>
+      <c r="E25" t="n">
+        <v>32.5</v>
       </c>
     </row>
     <row r="26">
@@ -8181,20 +7005,16 @@
           <t>西北工业大学</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>462.0</t>
-        </is>
+      <c r="C26" t="n">
+        <v>462</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
+      <c r="E26" t="n">
+        <v>33.4</v>
       </c>
     </row>
     <row r="27">
@@ -8206,20 +7026,16 @@
           <t>华南理工大学</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>444.2</t>
-        </is>
+      <c r="C27" t="n">
+        <v>444.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
+      <c r="E27" t="n">
+        <v>30.8</v>
       </c>
     </row>
     <row r="28">
@@ -8231,20 +7047,16 @@
           <t>吉林大学</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>439.1</t>
-        </is>
+      <c r="C28" t="n">
+        <v>439.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
+      <c r="E28" t="n">
+        <v>30.5</v>
       </c>
     </row>
     <row r="29">
@@ -8256,20 +7068,16 @@
           <t>电子科技大学</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>437.0</t>
-        </is>
+      <c r="C29" t="n">
+        <v>437</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>32.2</t>
-        </is>
+      <c r="E29" t="n">
+        <v>32.2</v>
       </c>
     </row>
     <row r="30">
@@ -8281,20 +7089,16 @@
           <t>湖南大学</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>435.5</t>
-        </is>
+      <c r="C30" t="n">
+        <v>435.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
+      <c r="E30" t="n">
+        <v>31.5</v>
       </c>
     </row>
     <row r="31">
@@ -8306,20 +7110,16 @@
           <t>中国农业大学</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>432.8</t>
-        </is>
+      <c r="C31" t="n">
+        <v>432.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>农业</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
+      <c r="E31" t="n">
+        <v>31.8</v>
       </c>
     </row>
   </sheetData>
@@ -8372,20 +7172,16 @@
           <t>清华大学</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>992.6</t>
-        </is>
+      <c r="C2" t="n">
+        <v>992.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>36.1</t>
-        </is>
+      <c r="E2" t="n">
+        <v>36.1</v>
       </c>
     </row>
     <row r="3">
@@ -8397,20 +7193,16 @@
           <t>北京大学</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>898.6</t>
-        </is>
+      <c r="C3" t="n">
+        <v>898.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>34.9</t>
-        </is>
+      <c r="E3" t="n">
+        <v>34.9</v>
       </c>
     </row>
     <row r="4">
@@ -8422,20 +7214,16 @@
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>793.8</t>
-        </is>
+      <c r="C4" t="n">
+        <v>793.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>34.9</t>
-        </is>
+      <c r="E4" t="n">
+        <v>34.9</v>
       </c>
     </row>
     <row r="5">
@@ -8447,20 +7235,16 @@
           <t>上海交通大学</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>776.3</t>
-        </is>
+      <c r="C5" t="n">
+        <v>776.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
+      <c r="E5" t="n">
+        <v>35.6</v>
       </c>
     </row>
     <row r="6">
@@ -8472,20 +7256,16 @@
           <t>复旦大学</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>697.0</t>
-        </is>
+      <c r="C6" t="n">
+        <v>697</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>36.6</t>
-        </is>
+      <c r="E6" t="n">
+        <v>36.6</v>
       </c>
     </row>
     <row r="7">
@@ -8497,20 +7277,16 @@
           <t>南京大学</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>656.1</t>
-        </is>
+      <c r="C7" t="n">
+        <v>656.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
+      <c r="E7" t="n">
+        <v>37.1</v>
       </c>
     </row>
     <row r="8">
@@ -8522,20 +7298,16 @@
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>578.4</t>
-        </is>
+      <c r="C8" t="n">
+        <v>578.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="E8" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -8547,20 +7319,16 @@
           <t>华中科技大学</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>578.0</t>
-        </is>
+      <c r="C9" t="n">
+        <v>578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>32.2</t>
-        </is>
+      <c r="E9" t="n">
+        <v>32.2</v>
       </c>
     </row>
     <row r="10">
@@ -8572,20 +7340,16 @@
           <t>武汉大学</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>577.3</t>
-        </is>
+      <c r="C10" t="n">
+        <v>577.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>31.7</t>
-        </is>
+      <c r="E10" t="n">
+        <v>31.7</v>
       </c>
     </row>
     <row r="11">
@@ -8597,20 +7361,16 @@
           <t>西安交通大学</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>566.4</t>
-        </is>
+      <c r="C11" t="n">
+        <v>566.4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>34.6</t>
-        </is>
+      <c r="E11" t="n">
+        <v>34.6</v>
       </c>
     </row>
     <row r="12">
@@ -8622,20 +7382,16 @@
           <t>中山大学</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>539.6</t>
-        </is>
+      <c r="C12" t="n">
+        <v>539.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
+      <c r="E12" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -8647,20 +7403,16 @@
           <t>北京航空航天大学</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>537.2</t>
-        </is>
+      <c r="C13" t="n">
+        <v>537.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>33.1</t>
-        </is>
+      <c r="E13" t="n">
+        <v>33.1</v>
       </c>
     </row>
     <row r="14">
@@ -8672,20 +7424,16 @@
           <t>东南大学</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>530.7</t>
-        </is>
+      <c r="C14" t="n">
+        <v>530.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>34.6</t>
-        </is>
+      <c r="E14" t="n">
+        <v>34.6</v>
       </c>
     </row>
     <row r="15">
@@ -8697,20 +7445,16 @@
           <t>北京理工大学</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>530.2</t>
-        </is>
+      <c r="C15" t="n">
+        <v>530.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>33.6</t>
-        </is>
+      <c r="E15" t="n">
+        <v>33.6</v>
       </c>
     </row>
     <row r="16">
@@ -8722,20 +7466,16 @@
           <t>四川大学</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>527.9</t>
-        </is>
+      <c r="C16" t="n">
+        <v>527.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="E16" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -8747,20 +7487,16 @@
           <t>哈尔滨工业大学</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>514.1</t>
-        </is>
+      <c r="C17" t="n">
+        <v>514.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
+      <c r="E17" t="n">
+        <v>32.6</v>
       </c>
     </row>
     <row r="18">
@@ -8772,20 +7508,16 @@
           <t>同济大学</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>509.6</t>
-        </is>
+      <c r="C18" t="n">
+        <v>509.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>35.2</t>
-        </is>
+      <c r="E18" t="n">
+        <v>35.2</v>
       </c>
     </row>
     <row r="19">
@@ -8797,20 +7529,16 @@
           <t>中国人民大学</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>508.3</t>
-        </is>
+      <c r="C19" t="n">
+        <v>508.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
+      <c r="E19" t="n">
+        <v>34.3</v>
       </c>
     </row>
     <row r="20">
@@ -8822,20 +7550,16 @@
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>501.4</t>
-        </is>
+      <c r="C20" t="n">
+        <v>501.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>32.1</t>
-        </is>
+      <c r="E20" t="n">
+        <v>32.1</v>
       </c>
     </row>
     <row r="21">
@@ -8847,20 +7571,16 @@
           <t>天津大学</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>491.5</t>
-        </is>
+      <c r="C21" t="n">
+        <v>491.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>33.1</t>
-        </is>
+      <c r="E21" t="n">
+        <v>33.1</v>
       </c>
     </row>
     <row r="22">
@@ -8872,20 +7592,16 @@
           <t>南开大学</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>481.8</t>
-        </is>
+      <c r="C22" t="n">
+        <v>481.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
+      <c r="E22" t="n">
+        <v>31.8</v>
       </c>
     </row>
     <row r="23">
@@ -8897,20 +7613,16 @@
           <t>山东大学</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>476.3</t>
-        </is>
+      <c r="C23" t="n">
+        <v>476.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
+      <c r="E23" t="n">
+        <v>29.7</v>
       </c>
     </row>
     <row r="24">
@@ -8922,20 +7634,16 @@
           <t>西北工业大学</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>459.9</t>
-        </is>
+      <c r="C24" t="n">
+        <v>459.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
+      <c r="E24" t="n">
+        <v>33.4</v>
       </c>
     </row>
     <row r="25">
@@ -8947,20 +7655,16 @@
           <t>厦门大学</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>458.2</t>
-        </is>
+      <c r="C25" t="n">
+        <v>458.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>32.1</t>
-        </is>
+      <c r="E25" t="n">
+        <v>32.1</v>
       </c>
     </row>
     <row r="26">
@@ -8972,20 +7676,16 @@
           <t>中南大学</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>456.1</t>
-        </is>
+      <c r="C26" t="n">
+        <v>456.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
+      <c r="E26" t="n">
+        <v>30.6</v>
       </c>
     </row>
     <row r="27">
@@ -8997,20 +7697,16 @@
           <t>吉林大学</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>443.7</t>
-        </is>
+      <c r="C27" t="n">
+        <v>443.7</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
+      <c r="E27" t="n">
+        <v>30.5</v>
       </c>
     </row>
     <row r="28">
@@ -9022,20 +7718,16 @@
           <t>中国农业大学</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>440.6</t>
-        </is>
+      <c r="C28" t="n">
+        <v>440.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>农业</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
+      <c r="E28" t="n">
+        <v>31.5</v>
       </c>
     </row>
     <row r="29">
@@ -9047,20 +7739,16 @@
           <t>大连理工大学</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>435.7</t>
-        </is>
+      <c r="C29" t="n">
+        <v>435.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>31.3</t>
-        </is>
+      <c r="E29" t="n">
+        <v>31.3</v>
       </c>
     </row>
     <row r="30">
@@ -9072,20 +7760,16 @@
           <t>华东师范大学</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>431.2</t>
-        </is>
+      <c r="C30" t="n">
+        <v>431.2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>师范</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
+      <c r="E30" t="n">
+        <v>32.6</v>
       </c>
     </row>
     <row r="31">
@@ -9097,20 +7781,16 @@
           <t>华南理工大学</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>430.6</t>
-        </is>
+      <c r="C31" t="n">
+        <v>430.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>理工</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
+      <c r="E31" t="n">
+        <v>30.4</v>
       </c>
     </row>
   </sheetData>
